--- a/assets/database_structure/case_list_structure.xlsx
+++ b/assets/database_structure/case_list_structure.xlsx
@@ -904,7 +904,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -925,6 +925,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1561,7 +1564,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="H5" s="7"/>
       <c r="I5" s="3"/>
     </row>
     <row r="6" ht="15.6" spans="1:9">
@@ -1664,7 +1667,7 @@
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="7"/>
+      <c r="F12" s="8"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -1692,7 +1695,7 @@
         <v>27</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="8"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="4"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -1707,7 +1710,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="8"/>
+      <c r="D15" s="9"/>
       <c r="E15" s="4"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -1722,22 +1725,22 @@
         <v>31</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row r="17" ht="16.8" spans="1:9">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="3"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="4"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -1745,16 +1748,16 @@
       <c r="I17" s="3"/>
     </row>
     <row r="18" ht="16.8" spans="1:9">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="8"/>
+      <c r="D18" s="9"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="9"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -1766,8 +1769,8 @@
       <c r="B19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
       <c r="E19" s="4"/>
       <c r="F19" s="5"/>
       <c r="G19" s="3"/>
@@ -1781,8 +1784,8 @@
       <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
       <c r="E20" s="4"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -1796,8 +1799,8 @@
       <c r="B21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="8"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="9"/>
       <c r="E21" s="4"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -1811,8 +1814,8 @@
       <c r="B22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
       <c r="E22" s="4"/>
       <c r="F22" s="5"/>
       <c r="G22" s="3"/>
@@ -1826,8 +1829,8 @@
       <c r="B23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
       <c r="E23" s="4"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -1835,90 +1838,90 @@
       <c r="I23" s="3"/>
     </row>
     <row r="24" ht="15.6" spans="1:9">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row r="25" ht="15.6" spans="1:9">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="9" t="s">
         <v>48</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row r="26" ht="15.6" spans="1:9">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="9" t="s">
         <v>50</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row r="27" ht="15.6" spans="1:9">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="9" t="s">
         <v>52</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
     </row>
     <row r="28" ht="15.6" spans="1:9">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="9" t="s">
         <v>54</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row r="29" ht="15.6" spans="1:9">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="9" t="s">
         <v>56</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -2420,518 +2423,518 @@
       <c r="I74" s="3"/>
     </row>
     <row r="105" ht="15.6" spans="1:6">
-      <c r="A105" s="8"/>
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
+      <c r="A105" s="9"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
+      <c r="E105" s="9"/>
     </row>
     <row r="106" ht="15.6" spans="1:6">
-      <c r="A106" s="8"/>
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="11"/>
+      <c r="A106" s="9"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="9"/>
+      <c r="F106" s="12"/>
     </row>
     <row r="107" ht="15.6" spans="1:6">
-      <c r="A107" s="8"/>
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="11"/>
+      <c r="A107" s="9"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="9"/>
+      <c r="F107" s="12"/>
     </row>
     <row r="108" ht="15.6" spans="1:6">
-      <c r="A108" s="8"/>
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="11"/>
+      <c r="A108" s="9"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="9"/>
+      <c r="F108" s="12"/>
     </row>
     <row r="109" ht="15.6" spans="1:6">
-      <c r="A109" s="8"/>
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="11"/>
+      <c r="A109" s="9"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9"/>
+      <c r="F109" s="12"/>
     </row>
     <row r="110" ht="15.6" spans="1:6">
-      <c r="A110" s="8"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="11"/>
+      <c r="A110" s="9"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="9"/>
+      <c r="F110" s="12"/>
     </row>
     <row r="111" ht="15.6" spans="1:6">
-      <c r="A111" s="8"/>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="11"/>
+      <c r="A111" s="9"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="9"/>
+      <c r="F111" s="12"/>
     </row>
     <row r="112" ht="15.6" spans="1:6">
-      <c r="A112" s="8"/>
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="11"/>
+      <c r="A112" s="9"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="9"/>
+      <c r="F112" s="12"/>
     </row>
     <row r="113" ht="15.6" spans="1:6">
-      <c r="A113" s="8"/>
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="11"/>
+      <c r="A113" s="9"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="9"/>
+      <c r="F113" s="12"/>
     </row>
     <row r="114" ht="15.6" spans="1:6">
-      <c r="A114" s="8"/>
-      <c r="B114" s="8"/>
-      <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="11"/>
+      <c r="A114" s="9"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="9"/>
+      <c r="F114" s="12"/>
     </row>
     <row r="115" ht="15.6" spans="1:6">
-      <c r="A115" s="8"/>
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="11"/>
+      <c r="A115" s="9"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
+      <c r="E115" s="9"/>
+      <c r="F115" s="12"/>
     </row>
     <row r="116" ht="15.6" spans="1:6">
-      <c r="A116" s="8"/>
-      <c r="B116" s="8"/>
-      <c r="C116" s="8"/>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
-      <c r="F116" s="11"/>
+      <c r="A116" s="9"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9"/>
+      <c r="E116" s="9"/>
+      <c r="F116" s="12"/>
     </row>
     <row r="117" ht="15.6" spans="1:6">
-      <c r="A117" s="8"/>
-      <c r="B117" s="8"/>
-      <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="11"/>
+      <c r="A117" s="9"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9"/>
+      <c r="E117" s="9"/>
+      <c r="F117" s="12"/>
     </row>
     <row r="118" ht="15.6" spans="1:6">
-      <c r="A118" s="8"/>
-      <c r="B118" s="8"/>
-      <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="11"/>
+      <c r="A118" s="9"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9"/>
+      <c r="E118" s="9"/>
+      <c r="F118" s="12"/>
     </row>
     <row r="119" ht="15.6" spans="1:6">
-      <c r="A119" s="8"/>
-      <c r="B119" s="8"/>
-      <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="11"/>
+      <c r="A119" s="9"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9"/>
+      <c r="E119" s="9"/>
+      <c r="F119" s="12"/>
     </row>
     <row r="120" ht="15.6" spans="1:6">
-      <c r="A120" s="8"/>
-      <c r="B120" s="8"/>
-      <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="11"/>
+      <c r="A120" s="9"/>
+      <c r="B120" s="9"/>
+      <c r="C120" s="9"/>
+      <c r="D120" s="9"/>
+      <c r="E120" s="9"/>
+      <c r="F120" s="12"/>
     </row>
     <row r="121" ht="15.6" spans="1:6">
-      <c r="A121" s="8"/>
-      <c r="B121" s="8"/>
-      <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="11"/>
+      <c r="A121" s="9"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9"/>
+      <c r="E121" s="9"/>
+      <c r="F121" s="12"/>
     </row>
     <row r="122" ht="15.6" spans="1:6">
-      <c r="A122" s="8"/>
-      <c r="B122" s="8"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="11"/>
+      <c r="A122" s="9"/>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="9"/>
+      <c r="F122" s="12"/>
     </row>
     <row r="123" ht="15.6" spans="1:6">
-      <c r="A123" s="8"/>
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="11"/>
+      <c r="A123" s="9"/>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
+      <c r="F123" s="12"/>
     </row>
     <row r="124" ht="15.6" spans="1:6">
-      <c r="A124" s="8"/>
-      <c r="B124" s="8"/>
-      <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
-      <c r="F124" s="11"/>
+      <c r="A124" s="9"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9"/>
+      <c r="D124" s="9"/>
+      <c r="E124" s="9"/>
+      <c r="F124" s="12"/>
     </row>
     <row r="125" ht="15.6" spans="1:6">
-      <c r="A125" s="8"/>
-      <c r="B125" s="8"/>
-      <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
-      <c r="E125" s="8"/>
-      <c r="F125" s="11"/>
+      <c r="A125" s="9"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="9"/>
+      <c r="F125" s="12"/>
     </row>
     <row r="126" ht="15.6" spans="1:6">
-      <c r="A126" s="8"/>
-      <c r="B126" s="8"/>
-      <c r="C126" s="8"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
+      <c r="A126" s="9"/>
+      <c r="B126" s="9"/>
+      <c r="C126" s="9"/>
+      <c r="D126" s="9"/>
+      <c r="E126" s="9"/>
     </row>
     <row r="127" ht="15.6" spans="1:6">
-      <c r="A127" s="8"/>
-      <c r="B127" s="8"/>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="11"/>
+      <c r="A127" s="9"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
+      <c r="E127" s="9"/>
+      <c r="F127" s="12"/>
     </row>
     <row r="128" ht="15.6" spans="1:6">
-      <c r="A128" s="8"/>
-      <c r="B128" s="8"/>
-      <c r="C128" s="8"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="11"/>
+      <c r="A128" s="9"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9"/>
+      <c r="E128" s="9"/>
+      <c r="F128" s="12"/>
     </row>
     <row r="129" ht="15.6" spans="1:6">
-      <c r="A129" s="8"/>
-      <c r="B129" s="8"/>
-      <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="11"/>
+      <c r="A129" s="9"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="9"/>
+      <c r="F129" s="12"/>
     </row>
     <row r="130" ht="15.6" spans="1:6">
-      <c r="A130" s="8"/>
-      <c r="B130" s="8"/>
-      <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="11"/>
+      <c r="A130" s="9"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
+      <c r="E130" s="9"/>
+      <c r="F130" s="12"/>
     </row>
     <row r="131" ht="15.6" spans="1:6">
-      <c r="A131" s="8"/>
-      <c r="B131" s="8"/>
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
+      <c r="A131" s="9"/>
+      <c r="B131" s="9"/>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9"/>
+      <c r="E131" s="9"/>
     </row>
     <row r="132" ht="15.6" spans="1:6">
-      <c r="A132" s="8"/>
-      <c r="B132" s="8"/>
-      <c r="C132" s="8"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="11"/>
+      <c r="A132" s="9"/>
+      <c r="B132" s="9"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9"/>
+      <c r="E132" s="9"/>
+      <c r="F132" s="12"/>
     </row>
     <row r="133" ht="15.6" spans="1:6">
-      <c r="A133" s="8"/>
-      <c r="B133" s="8"/>
-      <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="11"/>
+      <c r="A133" s="9"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="9"/>
+      <c r="E133" s="9"/>
+      <c r="F133" s="12"/>
     </row>
     <row r="134" ht="15.6" spans="1:6">
-      <c r="A134" s="8"/>
-      <c r="B134" s="8"/>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="11"/>
+      <c r="A134" s="9"/>
+      <c r="B134" s="9"/>
+      <c r="C134" s="9"/>
+      <c r="D134" s="9"/>
+      <c r="E134" s="9"/>
+      <c r="F134" s="12"/>
     </row>
     <row r="135" ht="15.6" spans="1:6">
-      <c r="A135" s="8"/>
-      <c r="B135" s="8"/>
-      <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="11"/>
+      <c r="A135" s="9"/>
+      <c r="B135" s="9"/>
+      <c r="C135" s="9"/>
+      <c r="D135" s="9"/>
+      <c r="E135" s="9"/>
+      <c r="F135" s="12"/>
     </row>
     <row r="136" ht="15.6" spans="1:6">
-      <c r="A136" s="8"/>
-      <c r="B136" s="8"/>
-      <c r="C136" s="8"/>
-      <c r="D136" s="8"/>
-      <c r="E136" s="8"/>
-      <c r="F136" s="11"/>
+      <c r="A136" s="9"/>
+      <c r="B136" s="9"/>
+      <c r="C136" s="9"/>
+      <c r="D136" s="9"/>
+      <c r="E136" s="9"/>
+      <c r="F136" s="12"/>
     </row>
     <row r="137" ht="15.6" spans="1:6">
-      <c r="A137" s="8"/>
-      <c r="B137" s="8"/>
-      <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="11"/>
+      <c r="A137" s="9"/>
+      <c r="B137" s="9"/>
+      <c r="C137" s="9"/>
+      <c r="D137" s="9"/>
+      <c r="E137" s="9"/>
+      <c r="F137" s="12"/>
     </row>
     <row r="138" ht="15.6" spans="1:6">
-      <c r="A138" s="8"/>
-      <c r="B138" s="8"/>
-      <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
-      <c r="E138" s="8"/>
-      <c r="F138" s="11"/>
+      <c r="A138" s="9"/>
+      <c r="B138" s="9"/>
+      <c r="C138" s="9"/>
+      <c r="D138" s="9"/>
+      <c r="E138" s="9"/>
+      <c r="F138" s="12"/>
     </row>
     <row r="176" ht="15.6" spans="1:5">
-      <c r="A176" s="8"/>
-      <c r="B176" s="8"/>
-      <c r="C176" s="8"/>
-      <c r="D176" s="8"/>
-      <c r="E176" s="8"/>
+      <c r="A176" s="9"/>
+      <c r="B176" s="9"/>
+      <c r="C176" s="9"/>
+      <c r="D176" s="9"/>
+      <c r="E176" s="9"/>
     </row>
     <row r="177" ht="15.6" spans="1:5">
-      <c r="A177" s="8"/>
-      <c r="B177" s="8"/>
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
+      <c r="A177" s="9"/>
+      <c r="B177" s="9"/>
+      <c r="C177" s="9"/>
+      <c r="D177" s="9"/>
+      <c r="E177" s="9"/>
     </row>
     <row r="178" ht="15.6" spans="1:5">
-      <c r="A178" s="8"/>
-      <c r="B178" s="8"/>
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
+      <c r="A178" s="9"/>
+      <c r="B178" s="9"/>
+      <c r="C178" s="9"/>
+      <c r="D178" s="9"/>
+      <c r="E178" s="9"/>
     </row>
     <row r="179" ht="15.6" spans="1:5">
-      <c r="A179" s="8"/>
-      <c r="B179" s="8"/>
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
+      <c r="A179" s="9"/>
+      <c r="B179" s="9"/>
+      <c r="C179" s="9"/>
+      <c r="D179" s="9"/>
+      <c r="E179" s="9"/>
     </row>
     <row r="180" ht="15.6" spans="1:5">
-      <c r="A180" s="8"/>
-      <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
-      <c r="D180" s="8"/>
-      <c r="E180" s="8"/>
+      <c r="A180" s="9"/>
+      <c r="B180" s="9"/>
+      <c r="C180" s="9"/>
+      <c r="D180" s="9"/>
+      <c r="E180" s="9"/>
     </row>
     <row r="181" ht="15.6" spans="1:5">
-      <c r="A181" s="8"/>
-      <c r="B181" s="8"/>
-      <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
-      <c r="E181" s="8"/>
+      <c r="A181" s="9"/>
+      <c r="B181" s="9"/>
+      <c r="C181" s="9"/>
+      <c r="D181" s="9"/>
+      <c r="E181" s="9"/>
     </row>
     <row r="182" ht="15.6" spans="1:5">
-      <c r="A182" s="8"/>
-      <c r="B182" s="8"/>
-      <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
+      <c r="A182" s="9"/>
+      <c r="B182" s="9"/>
+      <c r="C182" s="9"/>
+      <c r="D182" s="9"/>
+      <c r="E182" s="9"/>
     </row>
     <row r="183" ht="15.6" spans="1:5">
-      <c r="A183" s="8"/>
-      <c r="B183" s="8"/>
-      <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
-      <c r="E183" s="8"/>
+      <c r="A183" s="9"/>
+      <c r="B183" s="9"/>
+      <c r="C183" s="9"/>
+      <c r="D183" s="9"/>
+      <c r="E183" s="9"/>
     </row>
     <row r="184" ht="15.6" spans="1:5">
-      <c r="A184" s="8"/>
-      <c r="B184" s="8"/>
-      <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
-      <c r="E184" s="8"/>
+      <c r="A184" s="9"/>
+      <c r="B184" s="9"/>
+      <c r="C184" s="9"/>
+      <c r="D184" s="9"/>
+      <c r="E184" s="9"/>
     </row>
     <row r="185" ht="15.6" spans="1:5">
-      <c r="A185" s="8"/>
-      <c r="B185" s="8"/>
-      <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
-      <c r="E185" s="8"/>
+      <c r="A185" s="9"/>
+      <c r="B185" s="9"/>
+      <c r="C185" s="9"/>
+      <c r="D185" s="9"/>
+      <c r="E185" s="9"/>
     </row>
     <row r="186" ht="15.6" spans="1:5">
-      <c r="A186" s="8"/>
-      <c r="B186" s="8"/>
-      <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
-      <c r="E186" s="8"/>
+      <c r="A186" s="9"/>
+      <c r="B186" s="9"/>
+      <c r="C186" s="9"/>
+      <c r="D186" s="9"/>
+      <c r="E186" s="9"/>
     </row>
     <row r="187" ht="15.6" spans="1:5">
-      <c r="A187" s="8"/>
-      <c r="B187" s="8"/>
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
+      <c r="A187" s="9"/>
+      <c r="B187" s="9"/>
+      <c r="C187" s="9"/>
+      <c r="D187" s="9"/>
+      <c r="E187" s="9"/>
     </row>
     <row r="188" ht="15.6" spans="1:5">
-      <c r="A188" s="8"/>
-      <c r="B188" s="8"/>
-      <c r="C188" s="8"/>
-      <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
+      <c r="A188" s="9"/>
+      <c r="B188" s="9"/>
+      <c r="C188" s="9"/>
+      <c r="D188" s="9"/>
+      <c r="E188" s="9"/>
     </row>
     <row r="189" ht="15.6" spans="1:5">
-      <c r="A189" s="8"/>
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
-      <c r="E189" s="8"/>
+      <c r="A189" s="9"/>
+      <c r="B189" s="9"/>
+      <c r="C189" s="9"/>
+      <c r="D189" s="9"/>
+      <c r="E189" s="9"/>
     </row>
     <row r="190" ht="15.6" spans="1:5">
-      <c r="A190" s="8"/>
-      <c r="B190" s="8"/>
-      <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
+      <c r="A190" s="9"/>
+      <c r="B190" s="9"/>
+      <c r="C190" s="9"/>
+      <c r="D190" s="9"/>
+      <c r="E190" s="9"/>
     </row>
     <row r="191" ht="15.6" spans="1:5">
-      <c r="A191" s="8"/>
-      <c r="B191" s="8"/>
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
-      <c r="E191" s="8"/>
+      <c r="A191" s="9"/>
+      <c r="B191" s="9"/>
+      <c r="C191" s="9"/>
+      <c r="D191" s="9"/>
+      <c r="E191" s="9"/>
     </row>
     <row r="192" ht="15.6" spans="1:5">
-      <c r="A192" s="8"/>
-      <c r="B192" s="8"/>
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8"/>
+      <c r="A192" s="9"/>
+      <c r="B192" s="9"/>
+      <c r="C192" s="9"/>
+      <c r="D192" s="9"/>
+      <c r="E192" s="9"/>
     </row>
     <row r="193" ht="15.6" spans="1:5">
-      <c r="A193" s="8"/>
-      <c r="B193" s="8"/>
-      <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
-      <c r="E193" s="8"/>
+      <c r="A193" s="9"/>
+      <c r="B193" s="9"/>
+      <c r="C193" s="9"/>
+      <c r="D193" s="9"/>
+      <c r="E193" s="9"/>
     </row>
     <row r="194" ht="15.6" spans="1:5">
-      <c r="A194" s="8"/>
-      <c r="B194" s="8"/>
-      <c r="C194" s="8"/>
-      <c r="D194" s="8"/>
-      <c r="E194" s="8"/>
+      <c r="A194" s="9"/>
+      <c r="B194" s="9"/>
+      <c r="C194" s="9"/>
+      <c r="D194" s="9"/>
+      <c r="E194" s="9"/>
     </row>
     <row r="195" ht="15.6" spans="1:5">
-      <c r="A195" s="8"/>
-      <c r="B195" s="8"/>
-      <c r="C195" s="8"/>
-      <c r="D195" s="8"/>
-      <c r="E195" s="8"/>
+      <c r="A195" s="9"/>
+      <c r="B195" s="9"/>
+      <c r="C195" s="9"/>
+      <c r="D195" s="9"/>
+      <c r="E195" s="9"/>
     </row>
     <row r="196" ht="15.6" spans="1:5">
-      <c r="A196" s="8"/>
-      <c r="B196" s="8"/>
-      <c r="C196" s="8"/>
-      <c r="D196" s="8"/>
-      <c r="E196" s="8"/>
+      <c r="A196" s="9"/>
+      <c r="B196" s="9"/>
+      <c r="C196" s="9"/>
+      <c r="D196" s="9"/>
+      <c r="E196" s="9"/>
     </row>
     <row r="197" ht="15.6" spans="1:5">
-      <c r="A197" s="8"/>
-      <c r="B197" s="8"/>
-      <c r="C197" s="8"/>
-      <c r="D197" s="8"/>
-      <c r="E197" s="8"/>
+      <c r="A197" s="9"/>
+      <c r="B197" s="9"/>
+      <c r="C197" s="9"/>
+      <c r="D197" s="9"/>
+      <c r="E197" s="9"/>
     </row>
     <row r="198" ht="15.6" spans="1:5">
-      <c r="A198" s="8"/>
-      <c r="B198" s="8"/>
-      <c r="C198" s="8"/>
-      <c r="D198" s="8"/>
-      <c r="E198" s="8"/>
+      <c r="A198" s="9"/>
+      <c r="B198" s="9"/>
+      <c r="C198" s="9"/>
+      <c r="D198" s="9"/>
+      <c r="E198" s="9"/>
     </row>
     <row r="199" ht="15.6" spans="1:5">
-      <c r="A199" s="8"/>
-      <c r="B199" s="8"/>
-      <c r="C199" s="8"/>
-      <c r="D199" s="8"/>
-      <c r="E199" s="8"/>
+      <c r="A199" s="9"/>
+      <c r="B199" s="9"/>
+      <c r="C199" s="9"/>
+      <c r="D199" s="9"/>
+      <c r="E199" s="9"/>
     </row>
     <row r="200" ht="15.6" spans="1:5">
-      <c r="A200" s="8"/>
-      <c r="B200" s="8"/>
-      <c r="C200" s="8"/>
-      <c r="D200" s="8"/>
-      <c r="E200" s="8"/>
+      <c r="A200" s="9"/>
+      <c r="B200" s="9"/>
+      <c r="C200" s="9"/>
+      <c r="D200" s="9"/>
+      <c r="E200" s="9"/>
     </row>
     <row r="201" ht="15.6" spans="1:5">
-      <c r="A201" s="8"/>
-      <c r="B201" s="8"/>
-      <c r="C201" s="8"/>
-      <c r="D201" s="8"/>
-      <c r="E201" s="8"/>
+      <c r="A201" s="9"/>
+      <c r="B201" s="9"/>
+      <c r="C201" s="9"/>
+      <c r="D201" s="9"/>
+      <c r="E201" s="9"/>
     </row>
     <row r="202" ht="15.6" spans="1:5">
-      <c r="A202" s="8"/>
-      <c r="B202" s="8"/>
-      <c r="C202" s="8"/>
-      <c r="D202" s="8"/>
-      <c r="E202" s="8"/>
+      <c r="A202" s="9"/>
+      <c r="B202" s="9"/>
+      <c r="C202" s="9"/>
+      <c r="D202" s="9"/>
+      <c r="E202" s="9"/>
     </row>
     <row r="203" ht="15.6" spans="1:5">
-      <c r="A203" s="8"/>
-      <c r="B203" s="8"/>
-      <c r="C203" s="8"/>
-      <c r="D203" s="8"/>
-      <c r="E203" s="8"/>
+      <c r="A203" s="9"/>
+      <c r="B203" s="9"/>
+      <c r="C203" s="9"/>
+      <c r="D203" s="9"/>
+      <c r="E203" s="9"/>
     </row>
     <row r="204" ht="15.6" spans="1:5">
-      <c r="A204" s="8"/>
-      <c r="B204" s="8"/>
-      <c r="C204" s="8"/>
-      <c r="D204" s="8"/>
-      <c r="E204" s="8"/>
+      <c r="A204" s="9"/>
+      <c r="B204" s="9"/>
+      <c r="C204" s="9"/>
+      <c r="D204" s="9"/>
+      <c r="E204" s="9"/>
     </row>
     <row r="205" ht="15.6" spans="1:5">
-      <c r="A205" s="8"/>
-      <c r="B205" s="8"/>
-      <c r="C205" s="8"/>
-      <c r="D205" s="8"/>
-      <c r="E205" s="8"/>
+      <c r="A205" s="9"/>
+      <c r="B205" s="9"/>
+      <c r="C205" s="9"/>
+      <c r="D205" s="9"/>
+      <c r="E205" s="9"/>
     </row>
     <row r="206" ht="15.6" spans="1:5">
-      <c r="A206" s="8"/>
-      <c r="B206" s="8"/>
-      <c r="C206" s="8"/>
-      <c r="D206" s="8"/>
-      <c r="E206" s="8"/>
+      <c r="A206" s="9"/>
+      <c r="B206" s="9"/>
+      <c r="C206" s="9"/>
+      <c r="D206" s="9"/>
+      <c r="E206" s="9"/>
     </row>
     <row r="207" ht="15.6" spans="1:5">
-      <c r="A207" s="8"/>
-      <c r="B207" s="8"/>
-      <c r="C207" s="8"/>
-      <c r="D207" s="8"/>
-      <c r="E207" s="8"/>
+      <c r="A207" s="9"/>
+      <c r="B207" s="9"/>
+      <c r="C207" s="9"/>
+      <c r="D207" s="9"/>
+      <c r="E207" s="9"/>
     </row>
     <row r="208" ht="15.6" spans="1:5">
-      <c r="A208" s="8"/>
-      <c r="B208" s="8"/>
-      <c r="C208" s="8"/>
-      <c r="D208" s="8"/>
-      <c r="E208" s="8"/>
+      <c r="A208" s="9"/>
+      <c r="B208" s="9"/>
+      <c r="C208" s="9"/>
+      <c r="D208" s="9"/>
+      <c r="E208" s="9"/>
     </row>
     <row r="209" ht="15.6" spans="1:5">
-      <c r="A209" s="8"/>
-      <c r="B209" s="8"/>
-      <c r="C209" s="8"/>
-      <c r="D209" s="8"/>
-      <c r="E209" s="8"/>
+      <c r="A209" s="9"/>
+      <c r="B209" s="9"/>
+      <c r="C209" s="9"/>
+      <c r="D209" s="9"/>
+      <c r="E209" s="9"/>
     </row>
     <row r="210" ht="15.6" spans="1:5">
-      <c r="A210" s="8"/>
-      <c r="B210" s="8"/>
-      <c r="C210" s="8"/>
-      <c r="D210" s="8"/>
-      <c r="E210" s="8"/>
+      <c r="A210" s="9"/>
+      <c r="B210" s="9"/>
+      <c r="C210" s="9"/>
+      <c r="D210" s="9"/>
+      <c r="E210" s="9"/>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="3"/>
@@ -2941,88 +2944,88 @@
       <c r="E211" s="3"/>
     </row>
     <row r="212" ht="15.6" spans="1:5">
-      <c r="A212" s="8"/>
-      <c r="B212" s="8"/>
-      <c r="C212" s="8"/>
-      <c r="D212" s="8"/>
-      <c r="E212" s="8"/>
+      <c r="A212" s="9"/>
+      <c r="B212" s="9"/>
+      <c r="C212" s="9"/>
+      <c r="D212" s="9"/>
+      <c r="E212" s="9"/>
     </row>
     <row r="213" ht="15.6" spans="1:5">
-      <c r="A213" s="8"/>
-      <c r="B213" s="8"/>
-      <c r="C213" s="8"/>
-      <c r="D213" s="8"/>
-      <c r="E213" s="8"/>
+      <c r="A213" s="9"/>
+      <c r="B213" s="9"/>
+      <c r="C213" s="9"/>
+      <c r="D213" s="9"/>
+      <c r="E213" s="9"/>
     </row>
     <row r="214" ht="15.6" spans="1:5">
-      <c r="A214" s="8"/>
-      <c r="B214" s="8"/>
-      <c r="C214" s="8"/>
-      <c r="D214" s="8"/>
-      <c r="E214" s="8"/>
+      <c r="A214" s="9"/>
+      <c r="B214" s="9"/>
+      <c r="C214" s="9"/>
+      <c r="D214" s="9"/>
+      <c r="E214" s="9"/>
     </row>
     <row r="215" ht="15.6" spans="1:5">
-      <c r="A215" s="8"/>
-      <c r="B215" s="8"/>
-      <c r="C215" s="8"/>
-      <c r="D215" s="8"/>
-      <c r="E215" s="8"/>
+      <c r="A215" s="9"/>
+      <c r="B215" s="9"/>
+      <c r="C215" s="9"/>
+      <c r="D215" s="9"/>
+      <c r="E215" s="9"/>
     </row>
     <row r="216" ht="15.6" spans="1:5">
-      <c r="A216" s="8"/>
-      <c r="B216" s="8"/>
-      <c r="C216" s="8"/>
-      <c r="D216" s="8"/>
-      <c r="E216" s="8"/>
+      <c r="A216" s="9"/>
+      <c r="B216" s="9"/>
+      <c r="C216" s="9"/>
+      <c r="D216" s="9"/>
+      <c r="E216" s="9"/>
     </row>
     <row r="217" ht="15.6" spans="1:5">
-      <c r="A217" s="8"/>
-      <c r="B217" s="8"/>
-      <c r="C217" s="8"/>
-      <c r="D217" s="8"/>
-      <c r="E217" s="8"/>
+      <c r="A217" s="9"/>
+      <c r="B217" s="9"/>
+      <c r="C217" s="9"/>
+      <c r="D217" s="9"/>
+      <c r="E217" s="9"/>
     </row>
     <row r="218" ht="15.6" spans="1:5">
-      <c r="A218" s="8"/>
-      <c r="B218" s="8"/>
-      <c r="C218" s="8"/>
-      <c r="D218" s="8"/>
-      <c r="E218" s="8"/>
+      <c r="A218" s="9"/>
+      <c r="B218" s="9"/>
+      <c r="C218" s="9"/>
+      <c r="D218" s="9"/>
+      <c r="E218" s="9"/>
     </row>
     <row r="219" ht="15.6" spans="1:5">
-      <c r="A219" s="8"/>
-      <c r="B219" s="8"/>
-      <c r="C219" s="8"/>
-      <c r="D219" s="8"/>
-      <c r="E219" s="8"/>
+      <c r="A219" s="9"/>
+      <c r="B219" s="9"/>
+      <c r="C219" s="9"/>
+      <c r="D219" s="9"/>
+      <c r="E219" s="9"/>
     </row>
     <row r="220" ht="15.6" spans="1:5">
-      <c r="A220" s="8"/>
-      <c r="B220" s="8"/>
-      <c r="C220" s="8"/>
-      <c r="D220" s="8"/>
-      <c r="E220" s="8"/>
+      <c r="A220" s="9"/>
+      <c r="B220" s="9"/>
+      <c r="C220" s="9"/>
+      <c r="D220" s="9"/>
+      <c r="E220" s="9"/>
     </row>
     <row r="221" ht="15.6" spans="1:5">
-      <c r="A221" s="8"/>
-      <c r="B221" s="8"/>
-      <c r="C221" s="8"/>
-      <c r="D221" s="8"/>
-      <c r="E221" s="8"/>
+      <c r="A221" s="9"/>
+      <c r="B221" s="9"/>
+      <c r="C221" s="9"/>
+      <c r="D221" s="9"/>
+      <c r="E221" s="9"/>
     </row>
     <row r="222" ht="15.6" spans="1:5">
-      <c r="A222" s="8"/>
-      <c r="B222" s="8"/>
-      <c r="C222" s="8"/>
-      <c r="D222" s="8"/>
-      <c r="E222" s="8"/>
+      <c r="A222" s="9"/>
+      <c r="B222" s="9"/>
+      <c r="C222" s="9"/>
+      <c r="D222" s="9"/>
+      <c r="E222" s="9"/>
     </row>
     <row r="223" ht="15.6" spans="1:5">
-      <c r="A223" s="8"/>
-      <c r="B223" s="8"/>
-      <c r="C223" s="8"/>
-      <c r="D223" s="8"/>
-      <c r="E223" s="8"/>
+      <c r="A223" s="9"/>
+      <c r="B223" s="9"/>
+      <c r="C223" s="9"/>
+      <c r="D223" s="9"/>
+      <c r="E223" s="9"/>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="3"/>
